--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T14:33:17+00:00</t>
+    <t>2026-06-09T15:10:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:10:34+00:00</t>
+    <t>2026-06-09T15:32:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:32:43+00:00</t>
+    <t>2026-06-09T15:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:39:13+00:00</t>
+    <t>2026-06-09T15:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:42:49+00:00</t>
+    <t>2026-06-09T15:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:47:14+00:00</t>
+    <t>2026-06-09T19:07:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T19:07:13+00:00</t>
+    <t>2026-06-10T09:59:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:59:42+00:00</t>
+    <t>2026-06-10T10:03:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T10:03:35+00:00</t>
+    <t>2026-06-10T10:05:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T10:05:44+00:00</t>
+    <t>2026-06-10T10:08:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T10:08:12+00:00</t>
+    <t>2026-06-10T10:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T10:27:53+00:00</t>
+    <t>2026-06-10T12:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:22:45+00:00</t>
+    <t>2026-06-10T12:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:24:33+00:00</t>
+    <t>2026-06-10T12:26:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:26:33+00:00</t>
+    <t>2026-06-10T12:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:45:37+00:00</t>
+    <t>2026-06-10T12:57:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
+++ b/main/ig/ValueSet-jdv-ror-acte-specifique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:57:58+00:00</t>
+    <t>2026-07-07T12:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
